--- a/guillermocenso.xlsx
+++ b/guillermocenso.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6546" uniqueCount="1882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6539" uniqueCount="1882">
   <si>
     <t>Marcatemporal</t>
   </si>
@@ -5852,7 +5852,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5861,24 +5861,6 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -6267,7 +6249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DP120"/>
+  <dimension ref="A1:CG120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -6277,7 +6259,7 @@
     <col min="20" max="20" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6534,21 +6516,21 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:120" x14ac:dyDescent="0.25">
-      <c r="A2" s="24">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
         <v>45804.65284722222</v>
       </c>
       <c r="B2" t="s">
         <v>1881</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="23" t="s">
         <v>1859</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="7" t="s">
         <v>1881</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="7" t="s">
         <v>1860</v>
       </c>
       <c r="G2" s="1">
@@ -6557,73 +6539,73 @@
       <c r="H2" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="7" t="s">
         <v>90</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="9" t="s">
         <v>1861</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="9" t="s">
         <v>92</v>
       </c>
       <c r="O2">
         <v>3</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="9" t="s">
         <v>1862</v>
       </c>
       <c r="T2" t="s">
         <v>97</v>
       </c>
-      <c r="U2" s="13">
+      <c r="U2" s="7">
         <v>2006</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="9" t="s">
         <v>1863</v>
       </c>
       <c r="W2" t="s">
         <v>98</v>
       </c>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="18" t="s">
+      <c r="X2" s="7"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AB2" s="18" t="s">
+      <c r="AB2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18" t="s">
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12" t="s">
         <v>1864</v>
       </c>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="19" t="s">
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AI2" s="14" t="s">
         <v>209</v>
       </c>
       <c r="AJ2">
@@ -6632,22 +6614,22 @@
       <c r="AK2" s="1">
         <v>38899</v>
       </c>
-      <c r="AL2" s="27">
+      <c r="AL2" s="21">
         <v>40691</v>
       </c>
-      <c r="AM2" s="25" t="s">
+      <c r="AM2" s="19" t="s">
         <v>1865</v>
       </c>
-      <c r="AN2" s="28" t="s">
+      <c r="AN2" s="22" t="s">
         <v>1866</v>
       </c>
-      <c r="AO2" s="28" t="s">
+      <c r="AO2" s="22" t="s">
         <v>1867</v>
       </c>
-      <c r="AP2" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ2" s="25" t="s">
+      <c r="AP2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ2" s="19" t="s">
         <v>756</v>
       </c>
       <c r="AR2" t="s">
@@ -6656,37 +6638,37 @@
       <c r="AS2" t="s">
         <v>405</v>
       </c>
-      <c r="AT2" s="28" t="s">
+      <c r="AT2" s="22" t="s">
         <v>1866</v>
       </c>
-      <c r="AU2" s="28" t="s">
+      <c r="AU2" s="22" t="s">
         <v>1867</v>
       </c>
       <c r="AV2" t="s">
         <v>98</v>
       </c>
-      <c r="AW2" s="20">
+      <c r="AW2" s="14">
         <v>0</v>
       </c>
-      <c r="AX2" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="AY2" s="21" t="s">
+      <c r="AX2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" s="15" t="s">
         <v>1869</v>
       </c>
-      <c r="AZ2" s="22" t="s">
+      <c r="AZ2" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="BA2" s="25" t="s">
+      <c r="BA2" s="19" t="s">
         <v>1868</v>
       </c>
-      <c r="BB2" s="25" t="s">
+      <c r="BB2" s="19" t="s">
         <v>1870</v>
       </c>
-      <c r="BC2" s="28" t="s">
+      <c r="BC2" s="22" t="s">
         <v>1871</v>
       </c>
-      <c r="BD2" s="25" t="s">
+      <c r="BD2" s="19" t="s">
         <v>1868</v>
       </c>
       <c r="BE2" t="s">
@@ -6698,31 +6680,31 @@
       <c r="BG2" t="s">
         <v>90</v>
       </c>
-      <c r="BH2" s="25" t="s">
+      <c r="BH2" s="19" t="s">
         <v>1872</v>
       </c>
-      <c r="BI2" s="25" t="s">
+      <c r="BI2" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="BJ2" s="25" t="s">
+      <c r="BJ2" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="BK2" s="26" t="s">
+      <c r="BK2" s="20" t="s">
         <v>1880</v>
       </c>
-      <c r="BL2" s="21" t="s">
+      <c r="BL2" s="15" t="s">
         <v>1873</v>
       </c>
-      <c r="BM2" s="21" t="s">
+      <c r="BM2" s="15" t="s">
         <v>1873</v>
       </c>
-      <c r="BN2" s="25" t="s">
+      <c r="BN2" s="19" t="s">
         <v>1264</v>
       </c>
-      <c r="BO2" s="25" t="s">
+      <c r="BO2" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="BP2" s="30" t="s">
+      <c r="BP2" s="24" t="s">
         <v>1874</v>
       </c>
       <c r="BQ2" t="s">
@@ -6734,93 +6716,50 @@
       <c r="BS2" t="s">
         <v>90</v>
       </c>
-      <c r="BT2" s="25" t="s">
+      <c r="BT2" s="19" t="s">
         <v>1875</v>
       </c>
-      <c r="BU2" s="25" t="s">
+      <c r="BU2" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="BV2" s="25" t="s">
+      <c r="BV2" s="19" t="s">
         <v>1879</v>
       </c>
-      <c r="BW2" s="23" t="s">
+      <c r="BW2" s="17" t="s">
         <v>1876</v>
       </c>
-      <c r="BX2" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="BY2" s="25" t="s">
+      <c r="BX2" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="BY2" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="BZ2" s="21" t="s">
+      <c r="BZ2" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="CA2" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="CB2" s="25" t="s">
+      <c r="CA2" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="CB2" s="19" t="s">
         <v>1877</v>
       </c>
-      <c r="CC2" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="CD2" s="25" t="s">
+      <c r="CC2" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="CD2" s="19" t="s">
         <v>1878</v>
       </c>
-      <c r="CE2" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="CF2" s="25" t="s">
+      <c r="CE2" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF2" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="CI2" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="CJ2" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="CK2" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="CL2" s="25" t="s">
-        <v>1877</v>
-      </c>
-      <c r="CM2" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="CN2" s="25" t="s">
-        <v>1878</v>
-      </c>
-      <c r="CO2" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="CP2" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="CR2" s="10"/>
-      <c r="CS2" s="12"/>
-      <c r="CU2" s="10"/>
-      <c r="CV2" s="11"/>
-      <c r="CW2" s="7"/>
-      <c r="CX2" s="10"/>
-      <c r="CY2" s="10"/>
-      <c r="CZ2" s="10"/>
-      <c r="DA2" s="9"/>
-      <c r="DB2" s="9"/>
-      <c r="DC2" s="10"/>
-      <c r="DD2" s="7"/>
-      <c r="DE2" s="8"/>
-      <c r="DF2" s="10"/>
-      <c r="DG2" s="8"/>
-      <c r="DH2" s="10"/>
-      <c r="DI2" s="8"/>
-      <c r="DJ2" s="10"/>
-      <c r="DM2" s="14"/>
-      <c r="DN2" s="15"/>
-      <c r="DO2" s="14"/>
-      <c r="DP2" s="15"/>
+      <c r="CG2" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="3" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>83</v>
       </c>
@@ -6993,7 +6932,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -7172,7 +7111,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -7390,7 +7329,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -7575,7 +7514,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>201</v>
       </c>
@@ -7757,7 +7696,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>225</v>
       </c>
@@ -7888,7 +7827,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>241</v>
       </c>
@@ -7998,7 +7937,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>253</v>
       </c>
@@ -8192,7 +8131,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>277</v>
       </c>
@@ -8413,7 +8352,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="12" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>308</v>
       </c>
@@ -8598,7 +8537,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>327</v>
       </c>
@@ -8837,7 +8776,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>355</v>
       </c>
@@ -9025,7 +8964,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>368</v>
       </c>
@@ -9273,7 +9212,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>394</v>
       </c>

--- a/guillermocenso.xlsx
+++ b/guillermocenso.xlsx
@@ -6252,11 +6252,14 @@
   <dimension ref="A1:CG120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
     <col min="20" max="20" width="25.85546875" customWidth="1"/>
+    <col min="38" max="38" width="23" customWidth="1"/>
+    <col min="83" max="83" width="18.28515625" customWidth="1"/>
+    <col min="84" max="84" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" x14ac:dyDescent="0.25">
@@ -24809,6 +24812,9 @@
       </c>
       <c r="AK100" t="s">
         <v>1855</v>
+      </c>
+      <c r="AL100" s="1">
+        <v>41456</v>
       </c>
       <c r="AM100" t="s">
         <v>1585</v>
